--- a/Datos limpios/Pricing diario/2025/Girasol.xlsx
+++ b/Datos limpios/Pricing diario/2025/Girasol.xlsx
@@ -9486,298 +9486,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100D6CA5EAACE9DA04D9E421A617A76D009" ma:contentTypeVersion="19" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="854b0670eee28d8fa271d4f22cb9c97d">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="77131357-5c03-45fa-a80b-b9111bb46cb1" xmlns:ns3="d3f11db4-a96c-41b4-b8ec-902c72f52048" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b486ba09ce8a2fb19cc660d7edf32df4" ns2:_="" ns3:_="">
-    <xsd:import namespace="77131357-5c03-45fa-a80b-b9111bb46cb1"/>
-    <xsd:import namespace="d3f11db4-a96c-41b4-b8ec-902c72f52048"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:_Flow_SignoffStatus" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="77131357-5c03-45fa-a80b-b9111bb46cb1" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="10" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="11" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="12" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="13" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="14" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="15" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="17" nillable="true" ma:displayName="Location" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="_Flow_SignoffStatus" ma:index="20" nillable="true" ma:displayName="Estado de aprobación" ma:internalName="Estado_x0020_de_x0020_aprobaci_x00f3_n">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="21" nillable="true" ma:displayName="Length (seconds)" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="23" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Etiquetas de imagen" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="6ab20cb4-9c0f-41d2-89f3-02c382a657d6" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="25" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:description="" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="26" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="d3f11db4-a96c-41b4-b8ec-902c72f52048" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="18" nillable="true" ma:displayName="Compartido con" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="19" nillable="true" ma:displayName="Detalles de uso compartido" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="24" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ac6aff7b-77d9-4645-af3f-7b0008d975fa}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="d3f11db4-a96c-41b4-b8ec-902c72f52048">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Tipo de contenido"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Título"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_Flow_SignoffStatus xmlns="77131357-5c03-45fa-a80b-b9111bb46cb1" xsi:nil="true"/>
-    <TaxCatchAll xmlns="d3f11db4-a96c-41b4-b8ec-902c72f52048" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="77131357-5c03-45fa-a80b-b9111bb46cb1">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F9F8BA72-C7FE-4F25-B156-519B6EDF2D9E}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{32C1C225-3BFF-48F9-B3A2-1F780CAFCF14}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8625F02C-EB19-4677-901E-B86018DA4EF8}"/>
 </file>
--- a/Datos limpios/Pricing diario/2025/Girasol.xlsx
+++ b/Datos limpios/Pricing diario/2025/Girasol.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K246"/>
+  <dimension ref="A1:K267"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -9451,33 +9451,810 @@
         <v>45957</v>
       </c>
       <c r="B246">
-        <v>950</v>
+        <v>17061.72</v>
       </c>
       <c r="C246">
         <v>0</v>
       </c>
       <c r="D246">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="E246">
-        <v>950</v>
+        <v>16911.72</v>
       </c>
       <c r="F246">
-        <v>0</v>
+        <v>1377.62</v>
       </c>
       <c r="G246">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="H246">
         <v>0</v>
       </c>
       <c r="I246">
-        <v>0</v>
+        <v>1418.62</v>
       </c>
       <c r="J246">
-        <v>950</v>
+        <v>18330.34</v>
       </c>
       <c r="K246" t="inlineStr">
+        <is>
+          <t>GIRASOL</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="2">
+        <v>45958</v>
+      </c>
+      <c r="B247">
+        <v>14226.73</v>
+      </c>
+      <c r="C247">
+        <v>110</v>
+      </c>
+      <c r="D247">
+        <v>3588</v>
+      </c>
+      <c r="E247">
+        <v>10748.73</v>
+      </c>
+      <c r="F247">
+        <v>260</v>
+      </c>
+      <c r="G247">
+        <v>0</v>
+      </c>
+      <c r="H247">
+        <v>0</v>
+      </c>
+      <c r="I247">
+        <v>260</v>
+      </c>
+      <c r="J247">
+        <v>11008.73</v>
+      </c>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>GIRASOL</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="2">
+        <v>45959</v>
+      </c>
+      <c r="B248">
+        <v>10794.99</v>
+      </c>
+      <c r="C248">
+        <v>5.38</v>
+      </c>
+      <c r="D248">
+        <v>170</v>
+      </c>
+      <c r="E248">
+        <v>10630.37</v>
+      </c>
+      <c r="F248">
+        <v>140.57</v>
+      </c>
+      <c r="G248">
+        <v>0</v>
+      </c>
+      <c r="H248">
+        <v>0</v>
+      </c>
+      <c r="I248">
+        <v>140.57</v>
+      </c>
+      <c r="J248">
+        <v>10770.94</v>
+      </c>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>GIRASOL</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="2">
+        <v>45960</v>
+      </c>
+      <c r="B249">
+        <v>10922.15</v>
+      </c>
+      <c r="C249">
+        <v>10.9</v>
+      </c>
+      <c r="D249">
+        <v>560</v>
+      </c>
+      <c r="E249">
+        <v>10373.05</v>
+      </c>
+      <c r="F249">
+        <v>1145.51</v>
+      </c>
+      <c r="G249">
+        <v>0</v>
+      </c>
+      <c r="H249">
+        <v>0</v>
+      </c>
+      <c r="I249">
+        <v>1145.51</v>
+      </c>
+      <c r="J249">
+        <v>11518.56</v>
+      </c>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>GIRASOL</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="2">
+        <v>45961</v>
+      </c>
+      <c r="B250">
+        <v>8002.37</v>
+      </c>
+      <c r="C250">
+        <v>30.62</v>
+      </c>
+      <c r="D250">
+        <v>0</v>
+      </c>
+      <c r="E250">
+        <v>8032.99</v>
+      </c>
+      <c r="F250">
+        <v>0</v>
+      </c>
+      <c r="G250">
+        <v>0</v>
+      </c>
+      <c r="H250">
+        <v>0</v>
+      </c>
+      <c r="I250">
+        <v>0</v>
+      </c>
+      <c r="J250">
+        <v>8032.99</v>
+      </c>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>GIRASOL</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="2">
+        <v>45964</v>
+      </c>
+      <c r="B251">
+        <v>8369.34</v>
+      </c>
+      <c r="C251">
+        <v>0</v>
+      </c>
+      <c r="D251">
+        <v>0</v>
+      </c>
+      <c r="E251">
+        <v>8369.34</v>
+      </c>
+      <c r="F251">
+        <v>627.3099999999999</v>
+      </c>
+      <c r="G251">
+        <v>0</v>
+      </c>
+      <c r="H251">
+        <v>0</v>
+      </c>
+      <c r="I251">
+        <v>627.3099999999999</v>
+      </c>
+      <c r="J251">
+        <v>8996.65</v>
+      </c>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>GIRASOL</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="2">
+        <v>45965</v>
+      </c>
+      <c r="B252">
+        <v>30234.25</v>
+      </c>
+      <c r="C252">
+        <v>0</v>
+      </c>
+      <c r="D252">
+        <v>30.62</v>
+      </c>
+      <c r="E252">
+        <v>30203.63</v>
+      </c>
+      <c r="F252">
+        <v>1015</v>
+      </c>
+      <c r="G252">
+        <v>0</v>
+      </c>
+      <c r="H252">
+        <v>0</v>
+      </c>
+      <c r="I252">
+        <v>1015</v>
+      </c>
+      <c r="J252">
+        <v>31218.63</v>
+      </c>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>GIRASOL</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="2">
+        <v>45966</v>
+      </c>
+      <c r="B253">
+        <v>21777.76</v>
+      </c>
+      <c r="C253">
+        <v>0</v>
+      </c>
+      <c r="D253">
+        <v>1000</v>
+      </c>
+      <c r="E253">
+        <v>20777.76</v>
+      </c>
+      <c r="F253">
+        <v>1353.12</v>
+      </c>
+      <c r="G253">
+        <v>0</v>
+      </c>
+      <c r="H253">
+        <v>0</v>
+      </c>
+      <c r="I253">
+        <v>1353.12</v>
+      </c>
+      <c r="J253">
+        <v>22130.88</v>
+      </c>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>GIRASOL</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="2">
+        <v>45967</v>
+      </c>
+      <c r="B254">
+        <v>7089.08</v>
+      </c>
+      <c r="C254">
+        <v>0</v>
+      </c>
+      <c r="D254">
+        <v>13180</v>
+      </c>
+      <c r="E254">
+        <v>-6090.92</v>
+      </c>
+      <c r="F254">
+        <v>326.08</v>
+      </c>
+      <c r="G254">
+        <v>0</v>
+      </c>
+      <c r="H254">
+        <v>0</v>
+      </c>
+      <c r="I254">
+        <v>326.08</v>
+      </c>
+      <c r="J254">
+        <v>-5764.84</v>
+      </c>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>GIRASOL</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="2">
+        <v>45968</v>
+      </c>
+      <c r="B255">
+        <v>9011.860000000001</v>
+      </c>
+      <c r="C255">
+        <v>500</v>
+      </c>
+      <c r="D255">
+        <v>591</v>
+      </c>
+      <c r="E255">
+        <v>8920.860000000001</v>
+      </c>
+      <c r="F255">
+        <v>392.92</v>
+      </c>
+      <c r="G255">
+        <v>0</v>
+      </c>
+      <c r="H255">
+        <v>0</v>
+      </c>
+      <c r="I255">
+        <v>392.92</v>
+      </c>
+      <c r="J255">
+        <v>9313.780000000001</v>
+      </c>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>GIRASOL</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="2">
+        <v>45969</v>
+      </c>
+      <c r="B256">
+        <v>15</v>
+      </c>
+      <c r="C256">
+        <v>0</v>
+      </c>
+      <c r="D256">
+        <v>0</v>
+      </c>
+      <c r="E256">
+        <v>15</v>
+      </c>
+      <c r="F256">
+        <v>0</v>
+      </c>
+      <c r="G256">
+        <v>0</v>
+      </c>
+      <c r="H256">
+        <v>0</v>
+      </c>
+      <c r="I256">
+        <v>0</v>
+      </c>
+      <c r="J256">
+        <v>15</v>
+      </c>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>GIRASOL</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="2">
+        <v>45971</v>
+      </c>
+      <c r="B257">
+        <v>9390.530000000001</v>
+      </c>
+      <c r="C257">
+        <v>0</v>
+      </c>
+      <c r="D257">
+        <v>1070</v>
+      </c>
+      <c r="E257">
+        <v>8320.530000000001</v>
+      </c>
+      <c r="F257">
+        <v>139.7</v>
+      </c>
+      <c r="G257">
+        <v>0</v>
+      </c>
+      <c r="H257">
+        <v>0</v>
+      </c>
+      <c r="I257">
+        <v>139.7</v>
+      </c>
+      <c r="J257">
+        <v>8460.230000000001</v>
+      </c>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>GIRASOL</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="2">
+        <v>45972</v>
+      </c>
+      <c r="B258">
+        <v>15567.05</v>
+      </c>
+      <c r="C258">
+        <v>0</v>
+      </c>
+      <c r="D258">
+        <v>0</v>
+      </c>
+      <c r="E258">
+        <v>15567.05</v>
+      </c>
+      <c r="F258">
+        <v>346.18</v>
+      </c>
+      <c r="G258">
+        <v>0</v>
+      </c>
+      <c r="H258">
+        <v>0</v>
+      </c>
+      <c r="I258">
+        <v>346.18</v>
+      </c>
+      <c r="J258">
+        <v>15913.23</v>
+      </c>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>GIRASOL</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="2">
+        <v>45973</v>
+      </c>
+      <c r="B259">
+        <v>11267.99</v>
+      </c>
+      <c r="C259">
+        <v>0</v>
+      </c>
+      <c r="D259">
+        <v>236.69</v>
+      </c>
+      <c r="E259">
+        <v>11031.3</v>
+      </c>
+      <c r="F259">
+        <v>531.5599999999999</v>
+      </c>
+      <c r="G259">
+        <v>0</v>
+      </c>
+      <c r="H259">
+        <v>0</v>
+      </c>
+      <c r="I259">
+        <v>531.5599999999999</v>
+      </c>
+      <c r="J259">
+        <v>11562.86</v>
+      </c>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>GIRASOL</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="2">
+        <v>45974</v>
+      </c>
+      <c r="B260">
+        <v>7976.63</v>
+      </c>
+      <c r="C260">
+        <v>1950</v>
+      </c>
+      <c r="D260">
+        <v>0</v>
+      </c>
+      <c r="E260">
+        <v>9926.630000000001</v>
+      </c>
+      <c r="F260">
+        <v>66.59999999999999</v>
+      </c>
+      <c r="G260">
+        <v>0</v>
+      </c>
+      <c r="H260">
+        <v>0</v>
+      </c>
+      <c r="I260">
+        <v>66.59999999999999</v>
+      </c>
+      <c r="J260">
+        <v>9993.230000000001</v>
+      </c>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>GIRASOL</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="2">
+        <v>45975</v>
+      </c>
+      <c r="B261">
+        <v>9603.01</v>
+      </c>
+      <c r="C261">
+        <v>0</v>
+      </c>
+      <c r="D261">
+        <v>220</v>
+      </c>
+      <c r="E261">
+        <v>9383.01</v>
+      </c>
+      <c r="F261">
+        <v>624.0700000000001</v>
+      </c>
+      <c r="G261">
+        <v>0</v>
+      </c>
+      <c r="H261">
+        <v>0</v>
+      </c>
+      <c r="I261">
+        <v>624.0700000000001</v>
+      </c>
+      <c r="J261">
+        <v>10007.08</v>
+      </c>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>GIRASOL</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="2">
+        <v>45977</v>
+      </c>
+      <c r="B262">
+        <v>0</v>
+      </c>
+      <c r="C262">
+        <v>0</v>
+      </c>
+      <c r="D262">
+        <v>0</v>
+      </c>
+      <c r="E262">
+        <v>0</v>
+      </c>
+      <c r="F262">
+        <v>800.28</v>
+      </c>
+      <c r="G262">
+        <v>0</v>
+      </c>
+      <c r="H262">
+        <v>0</v>
+      </c>
+      <c r="I262">
+        <v>800.28</v>
+      </c>
+      <c r="J262">
+        <v>800.28</v>
+      </c>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>GIRASOL</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="2">
+        <v>45978</v>
+      </c>
+      <c r="B263">
+        <v>8514.66</v>
+      </c>
+      <c r="C263">
+        <v>155</v>
+      </c>
+      <c r="D263">
+        <v>0</v>
+      </c>
+      <c r="E263">
+        <v>8669.66</v>
+      </c>
+      <c r="F263">
+        <v>180</v>
+      </c>
+      <c r="G263">
+        <v>0</v>
+      </c>
+      <c r="H263">
+        <v>0</v>
+      </c>
+      <c r="I263">
+        <v>180</v>
+      </c>
+      <c r="J263">
+        <v>8849.66</v>
+      </c>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>GIRASOL</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="2">
+        <v>45979</v>
+      </c>
+      <c r="B264">
+        <v>7518.94</v>
+      </c>
+      <c r="C264">
+        <v>0</v>
+      </c>
+      <c r="D264">
+        <v>1100</v>
+      </c>
+      <c r="E264">
+        <v>6418.94</v>
+      </c>
+      <c r="F264">
+        <v>247.16</v>
+      </c>
+      <c r="G264">
+        <v>0</v>
+      </c>
+      <c r="H264">
+        <v>0</v>
+      </c>
+      <c r="I264">
+        <v>247.16</v>
+      </c>
+      <c r="J264">
+        <v>6666.099999999999</v>
+      </c>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>GIRASOL</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="2">
+        <v>45980</v>
+      </c>
+      <c r="B265">
+        <v>15124.94</v>
+      </c>
+      <c r="C265">
+        <v>600</v>
+      </c>
+      <c r="D265">
+        <v>12</v>
+      </c>
+      <c r="E265">
+        <v>15712.94</v>
+      </c>
+      <c r="F265">
+        <v>220</v>
+      </c>
+      <c r="G265">
+        <v>0</v>
+      </c>
+      <c r="H265">
+        <v>0</v>
+      </c>
+      <c r="I265">
+        <v>220</v>
+      </c>
+      <c r="J265">
+        <v>15932.94</v>
+      </c>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>GIRASOL</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="2">
+        <v>45981</v>
+      </c>
+      <c r="B266">
+        <v>9248.07</v>
+      </c>
+      <c r="C266">
+        <v>0</v>
+      </c>
+      <c r="D266">
+        <v>0</v>
+      </c>
+      <c r="E266">
+        <v>9248.07</v>
+      </c>
+      <c r="F266">
+        <v>442.21</v>
+      </c>
+      <c r="G266">
+        <v>0</v>
+      </c>
+      <c r="H266">
+        <v>0</v>
+      </c>
+      <c r="I266">
+        <v>442.21</v>
+      </c>
+      <c r="J266">
+        <v>9690.279999999999</v>
+      </c>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>GIRASOL</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="2">
+        <v>45982</v>
+      </c>
+      <c r="B267">
+        <v>1759.36</v>
+      </c>
+      <c r="C267">
+        <v>0</v>
+      </c>
+      <c r="D267">
+        <v>0</v>
+      </c>
+      <c r="E267">
+        <v>1759.36</v>
+      </c>
+      <c r="F267">
+        <v>496.94</v>
+      </c>
+      <c r="G267">
+        <v>0</v>
+      </c>
+      <c r="H267">
+        <v>0</v>
+      </c>
+      <c r="I267">
+        <v>496.94</v>
+      </c>
+      <c r="J267">
+        <v>2256.3</v>
+      </c>
+      <c r="K267" t="inlineStr">
         <is>
           <t>GIRASOL</t>
         </is>
